--- a/naver-place-crawler/results_health/영도구_헬스장.xlsx
+++ b/naver-place-crawler/results_health/영도구_헬스장.xlsx
@@ -417,13 +417,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="43" customWidth="1" min="7" max="7"/>
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>대시헬스/PT</t>
+          <t>오성피트니스 헬스&amp;필라테스 광복점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>barbiesue_@naver.com</t>
+          <t>hakunashop@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1322-0721</t>
+          <t>0507-1414-5265</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 361 3층</t>
+          <t>부산광역시 중구 광복로39번길 6 와이즈파크 5층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.ok114.co.kr/0514140721</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wdtozlo</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="n">
-        <v>164</v>
+        <v>49</v>
       </c>
       <c r="R2" t="n">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1647741601</t>
+          <t>2095838180</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1647741601</t>
+          <t>https://m.place.naver.com/place/2095838180</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>달라스짐 헬스&amp;PT</t>
+          <t>뉴타운헬스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dallasdo@naver.com</t>
+          <t>dudtlr01@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1370-9683</t>
+          <t>0507-1313-1339</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로35번길 56</t>
+          <t>부산광역시 영도구 절영로 58 7,.8층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dallasdo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,12 +694,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -711,17 +715,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>230</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>691</v>
+        <v>14</v>
       </c>
       <c r="R3" t="n">
-        <v>921</v>
+        <v>16</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +734,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1317827209</t>
+          <t>1283066751</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1317827209</t>
+          <t>https://m.place.naver.com/place/1283066751</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>뉴타운헬스</t>
+          <t>제이엘피트니스 영도점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ezhwan3419@naver.com</t>
+          <t>jlfitness711@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1313-1339</t>
+          <t>0507-1350-8253</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 58 7,.8층</t>
+          <t>부산광역시 영도구 남항서로 123 정림위더스하임 지하1층, 2층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://jlfitness711.wixsite.com/jl-fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -784,20 +788,24 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4vtvk</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -805,17 +813,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>295</v>
       </c>
       <c r="Q4" t="n">
-        <v>14</v>
+        <v>381</v>
       </c>
       <c r="R4" t="n">
-        <v>16</v>
+        <v>676</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,24 +832,24 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1283066751</t>
+          <t>1919075473</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1283066751</t>
+          <t>https://m.place.naver.com/place/1919075473</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>장소대여</t>
+          <t>공유누리 개방자원</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -924,41 +932,41 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>헬스보이짐 롯데백화점광복점</t>
+          <t>더미라클짐</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>healthboygym33@naver.com</t>
+          <t>dreams1385@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1447-4479</t>
+          <t>0507-1469-7915</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중앙대로 2 롯데백화점 광복점 아쿠아몰 7,8층 헬스보이짐</t>
+          <t>부산광역시 중구 광복중앙로 34 시티프라자 4F 더미라클짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/healthboygym33</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -968,20 +976,24 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w46hzl</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -993,13 +1005,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>149</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>329</v>
+        <v>22</v>
       </c>
       <c r="R6" t="n">
-        <v>478</v>
+        <v>29</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1008,51 +1020,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1023314986</t>
+          <t>1670512402</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023314986</t>
+          <t>https://m.place.naver.com/place/1670512402</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피트니스넘버원 헬스&amp;PT 남포중앙점</t>
+          <t>킹콩짐</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>f1fitness_nampo@naver.com</t>
+          <t>w306w@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1422-1605</t>
+          <t>051-231-9002</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 중구 중앙대로20번길 3 동방빌딩 별관 2층</t>
+          <t>부산광역시 서구 보수대로 15 봄여름가을겨울 아파트 상가 202호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/f1fitness_nampo</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1062,12 +1074,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1087,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="Q7" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="R7" t="n">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1102,51 +1114,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2056360077</t>
+          <t>35372548</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2056360077</t>
+          <t>https://m.place.naver.com/place/35372548</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>오성피트니스 헬스&amp;PT 남포점</t>
+          <t>피에스 피트니스 P.T &amp; 필라테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>osung_nampo@naver.com</t>
+          <t>ps_gym_14@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1360-5555</t>
+          <t>0507-1436-6123</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 서구 보수대로 27 경동리인타워 상가2층</t>
+          <t>부산광역시 영도구 절영로 531 우리마트 2층 피에스 피트니스</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/osungfitness_nampo/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1156,7 +1168,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1166,10 +1178,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4dyna</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1181,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>488</v>
+        <v>337</v>
       </c>
       <c r="Q8" t="n">
-        <v>1140</v>
+        <v>524</v>
       </c>
       <c r="R8" t="n">
-        <v>1628</v>
+        <v>861</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1196,51 +1212,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1593613950</t>
+          <t>1749447088</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593613950</t>
+          <t>https://m.place.naver.com/place/1749447088</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>메이저피트니스 프리미엄 헬스/PT</t>
+          <t>레핏짐 피트니스 헬스&amp;PT 초량점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>majorhun@naver.com</t>
+          <t>lefitgym0508@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>051-466-9260</t>
+          <t>0507-1481-0509</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 중구 대청로 109 3층 메이저피트니스</t>
+          <t>부산광역시 동구 중앙대로 193 마린리더스타워 3층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/majorhun</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1250,23 +1266,27 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wd8v9kk</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1275,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>531</v>
+        <v>224</v>
       </c>
       <c r="Q9" t="n">
-        <v>233</v>
+        <v>151</v>
       </c>
       <c r="R9" t="n">
-        <v>764</v>
+        <v>375</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1290,51 +1310,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1141545337</t>
+          <t>1023178095</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1141545337</t>
+          <t>https://m.place.naver.com/place/1023178095</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모션업 피트니스 헬스&amp;PT 남포동점</t>
+          <t>스타짐중앙점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>motionup_fitness@naver.com</t>
+          <t>stargymjb@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1453-1915</t>
+          <t>0507-1350-5964</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 중구 광복중앙로 32-1 4층</t>
+          <t>부산광역시 중구 중앙대로 96 흥우빌딩 B1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/motionup_nampodong/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,7 +1364,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1354,10 +1374,14 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wc5mey</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,13 +1393,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="Q10" t="n">
-        <v>483</v>
+        <v>86</v>
       </c>
       <c r="R10" t="n">
-        <v>820</v>
+        <v>396</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,51 +1408,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1593151857</t>
+          <t>31093542</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1593151857</t>
+          <t>https://m.place.naver.com/place/31093542</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>레핏짐 피트니스 헬스&amp;PT 초량점</t>
+          <t>호연 휘트니스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lefitgym0508@naver.com</t>
+          <t>jfitnessconsulting@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1481-0509</t>
+          <t>0507-1307-8920</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 동구 중앙대로 193 마린리더스타워 3층</t>
+          <t>부산광역시 영도구 태종로 98 6층 호연휘트니스</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/lefitgym/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,7 +1462,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1448,10 +1472,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zq6q</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1463,13 +1491,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>218</v>
+        <v>528</v>
       </c>
       <c r="Q11" t="n">
-        <v>157</v>
+        <v>386</v>
       </c>
       <c r="R11" t="n">
-        <v>375</v>
+        <v>914</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,61 +1506,61 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1023178095</t>
+          <t>1958145545</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1023178095</t>
+          <t>https://m.place.naver.com/place/1958145545</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>워너짐 헬스&amp;PT 부민점</t>
+          <t>오케이피트니스 남포점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>wannagym87@naver.com</t>
+          <t>okfitness-jungang@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1380-1517</t>
+          <t>0507-1336-0362</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>부산광역시 서구 구덕로 216 명보빌딩2층</t>
+          <t>부산광역시 중구 해관로 19-1 2층 (돌쇠장작구이 건물)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/wannagym87</t>
+          <t>https://www.okfitness.co.kr/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1542,13 +1570,17 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcjqjv2</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1557,10 +1589,10 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>289</v>
+        <v>192</v>
       </c>
       <c r="Q12" t="n">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="R12" t="n">
         <v>344</v>
@@ -1572,47 +1604,51 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1240460909</t>
+          <t>1293786707</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1240460909</t>
+          <t>https://m.place.naver.com/place/1293786707</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>조아짐 영도</t>
+          <t>피트니스코리아</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>joagym9696@naver.com</t>
+          <t>pys2002lyh@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1475-9683</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항서로 52 3층</t>
+          <t>부산광역시 서구 충무대로275번길 20 에코펠리스 지하1층 B101호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/joagym_yeongdo</t>
+          <t>https://blog.naver.com/pys2002lyh</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1627,7 +1663,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1647,13 +1683,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="Q13" t="n">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="R13" t="n">
-        <v>68</v>
+        <v>183</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1662,51 +1698,51 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1388144636</t>
+          <t>1894030831</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1388144636</t>
+          <t>https://m.place.naver.com/place/1894030831</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>피에스 피트니스 P.T &amp; 필라테스</t>
+          <t>굿바디휘트니스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ps_gym_14@naver.com</t>
+          <t>goodbodyfitness_yd@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0507-1436-6123</t>
+          <t>0507-1316-9825</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 절영로 531 우리마트 2층 피에스 피트니스</t>
+          <t>부산광역시 영도구 동삼로 56 한나타워 501호</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ps_gym_14</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1716,20 +1752,24 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5x4km</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>X</t>
@@ -1741,13 +1781,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>322</v>
+        <v>262</v>
       </c>
       <c r="Q14" t="n">
-        <v>519</v>
+        <v>220</v>
       </c>
       <c r="R14" t="n">
-        <v>841</v>
+        <v>482</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
@@ -1756,51 +1796,51 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1749447088</t>
+          <t>21302860</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1749447088</t>
+          <t>https://m.place.naver.com/place/21302860</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>굿바디휘트니스</t>
+          <t>헬스보이짐 롯데백화점광복점</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>goodbodyfitness_yd@naver.com</t>
+          <t>healthboygym33@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0507-1316-9825</t>
+          <t>0507-1447-4479</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 56 한나타워 501호</t>
+          <t>부산광역시 중구 중앙대로 2 롯데백화점 광복점 아쿠아몰 7,8층 헬스보이짐</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/goodbodyfitness_yd</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1810,20 +1850,24 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w465qg</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>X</t>
@@ -1835,13 +1879,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>262</v>
+        <v>150</v>
       </c>
       <c r="Q15" t="n">
-        <v>219</v>
+        <v>328</v>
       </c>
       <c r="R15" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
@@ -1850,51 +1894,51 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>21302860</t>
+          <t>1023314986</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21302860</t>
+          <t>https://m.place.naver.com/place/1023314986</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>호연 휘트니스</t>
+          <t>피트니스넘버원 헬스&amp;PT 남포중앙점</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>blogbytim@naver.com</t>
+          <t>f1fitness_nampo@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0507-1307-8920</t>
+          <t>0507-1422-1605</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 태종로 98 6층 호연휘트니스</t>
+          <t>부산광역시 중구 중앙대로20번길 3 동방빌딩 별관 2층</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/blogbytim</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1904,20 +1948,24 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w1az8cc</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr">
         <is>
           <t>X</t>
@@ -1929,13 +1977,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>524</v>
+        <v>59</v>
       </c>
       <c r="Q16" t="n">
-        <v>387</v>
+        <v>38</v>
       </c>
       <c r="R16" t="n">
-        <v>911</v>
+        <v>97</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -1944,66 +1992,66 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1958145545</t>
+          <t>2056360077</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1958145545</t>
+          <t>https://m.place.naver.com/place/2056360077</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>제이엘피트니스 영도점</t>
+          <t>굿모닝휘트니스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>on180102@naver.com</t>
+          <t>pinelemon@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0507-1350-8253</t>
+          <t>051-253-3585</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 남항서로 123 정림위더스하임 지하1층, 2층</t>
+          <t>부산광역시 중구 대청로 71</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://jlfitness711.wixsite.com/jl-fitness</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2019,17 +2067,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>294</v>
+        <v>14</v>
       </c>
       <c r="Q17" t="n">
-        <v>381</v>
+        <v>7</v>
       </c>
       <c r="R17" t="n">
-        <v>675</v>
+        <v>21</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2038,56 +2086,56 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1919075473</t>
+          <t>1902768143</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1919075473</t>
+          <t>https://m.place.naver.com/place/1902768143</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>오케이피트니스 영도 1호점</t>
+          <t>부평헬스장</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>okfitness-yeongdo@naver.com</t>
+          <t>timegym12@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0507-1334-8674</t>
+          <t>051-246-2961</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 와치로 252 선프라자 B1, 4F</t>
+          <t>부산광역시 중구 부평1길 48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.okfitness.co.kr/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2097,7 +2145,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2108,22 +2156,22 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>398</v>
+        <v>16</v>
       </c>
       <c r="Q18" t="n">
-        <v>302</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>700</v>
+        <v>18</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2132,24 +2180,24 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1785305399</t>
+          <t>16425145</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1785305399</t>
+          <t>https://m.place.naver.com/place/16425145</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2211,13 +2259,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="Q19" t="n">
         <v>52</v>
       </c>
       <c r="R19" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2236,41 +2284,41 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>제네시스피트니스</t>
+          <t>워너짐 헬스&amp;PT 부민점</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>an4041@naver.com</t>
+          <t>wannagym87@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0507-1400-1159</t>
+          <t>0507-1380-1517</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>부산광역시 영도구 동삼로 12 제네시스헬스클럽</t>
+          <t>부산광역시 서구 구덕로 216 명보빌딩2층</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/an4041</t>
+          <t>https://blog.naver.com/wannagym87</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2301,17 +2349,17 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>70</v>
+        <v>289</v>
       </c>
       <c r="Q20" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="R20" t="n">
-        <v>171</v>
+        <v>344</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
@@ -2320,61 +2368,61 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>37816428</t>
+          <t>1240460909</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37816428</t>
+          <t>https://m.place.naver.com/place/1240460909</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>크로스핏 롱스톤</t>
+          <t>오케이피트니스 영도 1호점</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>marcio75@naver.com</t>
+          <t>okfitness-yeongdo@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1300-8725</t>
+          <t>0507-1334-8674</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>부산광역시 동구 중앙대로180번길 13 프레지던트 오피스텔 지하1층</t>
+          <t>부산광역시 영도구 와치로 252 선프라자 B1, 4F</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/marcio75</t>
+          <t>https://www.okfitness.co.kr/</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2390,41 +2438,2759 @@
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P21" t="n">
+        <v>411</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>304</v>
+      </c>
+      <c r="R21" t="n">
+        <v>715</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1785305399</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1785305399</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>달라스짐 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>dallasdo@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0507-1370-9683</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>부산광역시 영도구 절영로35번길 56</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dallasdo</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>232</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>693</v>
+      </c>
+      <c r="R22" t="n">
+        <v>925</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1317827209</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1317827209</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>제네시스피트니스</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>an4041@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1400-1159</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>부산광역시 영도구 동삼로 12 제네시스헬스클럽</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/an4041</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>101</v>
+      </c>
+      <c r="R23" t="n">
+        <v>171</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>37816428</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37816428</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>리복크로스핏 세찬</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>stk791@naver.com</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0507-1327-3081</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 구덕로 90 지하2층 크로스핏세찬</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>http://cfbusan.cafe24.com/</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>57</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>78</v>
+      </c>
+      <c r="R24" t="n">
+        <v>135</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>33831491</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/33831491</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>메이저피트니스 프리미엄 헬스/PT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>majorhun@naver.com</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>051-466-9260</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 대청로 109 3층 메이저피트니스</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/majorhun</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>533</v>
+      </c>
+      <c r="Q25" t="n">
         <v>231</v>
       </c>
-      <c r="Q21" t="n">
-        <v>160</v>
-      </c>
-      <c r="R21" t="n">
-        <v>391</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
+      <c r="R25" t="n">
+        <v>764</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>1141545337</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1141545337</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>플렉스짐 헬스 PT &amp; 요가플렉스</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>bka2471022@naver.com</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0507-1399-6015</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 보수대로 71 한미S빌딩 2층 3층</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yogaflex_bumin</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>78</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>366</v>
+      </c>
+      <c r="R26" t="n">
+        <v>444</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>1406407260</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1406407260</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>테크노짐헬스</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>k10m10w10@naver.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 대영로 235</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>19</v>
+      </c>
+      <c r="R27" t="n">
+        <v>19</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1766479151</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1766479151</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>올림포스짐 토성점 헬스/PT</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>olympos-gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0507-1312-4821</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로 147 3층, 4층</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/olympos_gym_korea</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>402</v>
+      </c>
+      <c r="R28" t="n">
+        <v>452</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1037271910</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1037271910</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>오팀 퍼스널 트레이닝 센터 헬스/PT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>oteam_pt@naver.com</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0507-1333-6246</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 광복중앙로 2 4층</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://link.inpock.co.kr/oteampt</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w47d0u</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>453</v>
+      </c>
+      <c r="R29" t="n">
+        <v>578</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1430358858</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1430358858</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>크로스핏 롱스톤</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>marcio75@naver.com</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0507-1300-8725</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 중앙대로180번길 13 프레지던트 오피스텔 지하1층</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>241</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>161</v>
+      </c>
+      <c r="R30" t="n">
+        <v>402</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>410246767</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/410246767</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>임펄스 짐</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>aicy18mm@naver.com</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0507-1325-9909</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 대청로 60 월드벨리 8층 임펄스짐</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>92</v>
+      </c>
+      <c r="R31" t="n">
+        <v>111</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>1873202957</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1873202957</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>썸바디</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>sky1250ww@naver.com</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>051-242-2004</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 해관로 3 스타빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/sky1250ww</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>14</v>
+      </c>
+      <c r="R32" t="n">
+        <v>21</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>35342421</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/35342421</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>부산아카데미헬스</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ykbacademy@naver.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 광복로35번길 7</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>16911598</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16911598</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>모션업 피트니스 헬스&amp;PT 남포동점</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>motionup_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0507-1453-1915</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 광복중앙로 32-1 4층</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/motionup_nampodong/</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>340</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>486</v>
+      </c>
+      <c r="R34" t="n">
+        <v>826</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>1593151857</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593151857</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>대시헬스/PT</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>barbiesue_@naver.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0507-1322-0721</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>부산광역시 영도구 태종로 361 3층</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>https://www.ok114.co.kr/0514140721</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>51</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>164</v>
+      </c>
+      <c r="R35" t="n">
+        <v>215</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>1647741601</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1647741601</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>바디업헬스</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>lucky1230kr@naver.com</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>051-465-6700</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 대영로 235 제일빌딩 10층</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/lucky1230kr</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>14</v>
+      </c>
+      <c r="R36" t="n">
+        <v>111</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>16440173</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16440173</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>포시즌헬스</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>fseason1636@naver.com</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0507-1467-3309</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로 119 3,4층</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>7</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>1379172231</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1379172231</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>오성피트니스 헬스&amp;PT 남포점</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>osung_nampo@naver.com</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0507-1360-5555</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 보수대로 27 경동리인타워 상가2층</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/osungfitness_nampo/</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>492</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1146</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1638</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>1593613950</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1593613950</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>목욕탕,사우나</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>마린목욕탕</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>aoop09@naver.com</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>051-469-2777</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 충장대로9번길 52 마린센타지하 1 층</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>10</v>
+      </c>
+      <c r="R39" t="n">
+        <v>24</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>16408025</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16408025</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>럭키네피티</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>emrdkafl@naver.com</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로 150 3층 럭키네피티</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>34</v>
+      </c>
+      <c r="R40" t="n">
+        <v>34</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>1524339103</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1524339103</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>팬텀 PT &amp; 레이스 필라테스 용호점</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>juyoung6757@naver.com</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0507-1418-9678</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>부산광역시 남구 용호로 225-1 2층</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/juyoung6757</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>104</v>
+      </c>
+      <c r="R41" t="n">
+        <v>134</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>1803256202</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1803256202</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>퍼스널짐</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>personal___gym@naver.com</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0507-1474-0802</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 대영로85번길 14 3층</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>http://http//xn--p50b964aohf5wk.com/</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>58</v>
+      </c>
+      <c r="R42" t="n">
+        <v>105</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>1596917839</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1596917839</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>조아짐 영도</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>joagym9696@naver.com</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>부산광역시 영도구 남항서로 52 3층</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>67</v>
+      </c>
+      <c r="R43" t="n">
+        <v>68</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>1388144636</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1388144636</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>여성전용 지니 트레이닝</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>youjin9658@naver.com</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0507-1363-9658</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 구덕로148번길 30 1층</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>33</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>33</v>
+      </c>
+      <c r="R44" t="n">
+        <v>66</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>1532047693</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1532047693</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>오성피트니스 대신점</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>momjjang_@naver.com</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>0507-1439-5553</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>부산광역시 서구 보수대로 198-1 1, 2층 오성피트니스</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/momjjang_</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>143</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>487</v>
+      </c>
+      <c r="R45" t="n">
+        <v>630</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>1944190273</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1944190273</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>메디핏 남포점</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>pacemaker_034@naver.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>070-7380-8930</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 구덕로 30-1 피닉스동물병원 6층</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/pacemaker_034</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>482</v>
+      </c>
+      <c r="R46" t="n">
+        <v>505</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>32372647</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/32372647</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>로이디자인</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>roi_id@naver.com</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0507-1439-3530</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>부산광역시 동구 중앙대로196번길 6-7 405호E01호</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>4</v>
+      </c>
+      <c r="R47" t="n">
+        <v>5</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>1111450674</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1111450674</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>메디앤컬필라테스 롯데광복점</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>medincurlgb@naver.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0507-1338-3966</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 중앙대로 2 롯데백화점 광복점 9층</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/medincurlgb</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>265</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>311</v>
+      </c>
+      <c r="R48" t="n">
+        <v>576</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>1827449851</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1827449851</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>필라테스365 토성점</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>seo_sujung@naver.com</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0507-1364-0125</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>부산광역시 중구 보수대로 82 골든시티 14층</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/pilates365.tosung</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>203</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>51</v>
+      </c>
+      <c r="R49" t="n">
+        <v>254</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>1484903297</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1484903297</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>필라테스</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>메디앤컬필라테스 용호데시앙점</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>medincurl_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>sample@sample.or.kr</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0507-1428-3386</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>부산광역시 남구 용호로 213 3층</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>http://medincurl.com/</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>216</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>58</v>
+      </c>
+      <c r="R50" t="n">
+        <v>274</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>1170400362</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1170400362</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
